--- a/research/traditional_assets/database/data/philippines/philippines_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06795</v>
+        <v>0.128</v>
       </c>
       <c r="E2">
-        <v>-0.03965</v>
+        <v>0.2045</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>52.16</v>
+        <v>119.4</v>
       </c>
       <c r="L2">
-        <v>0.2071485305798252</v>
+        <v>0.3851612903225807</v>
       </c>
       <c r="M2">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="N2">
-        <v>0.03567405182125422</v>
+        <v>0.03448275862068965</v>
       </c>
       <c r="O2">
-        <v>0.3642638036809816</v>
+        <v>0.1381909547738693</v>
       </c>
       <c r="P2">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Q2">
-        <v>0.03567405182125422</v>
+        <v>0.03448275862068965</v>
       </c>
       <c r="R2">
-        <v>0.3642638036809816</v>
+        <v>0.1381909547738693</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>690.7</v>
+        <v>345.6</v>
       </c>
       <c r="V2">
-        <v>1.296845662786331</v>
+        <v>0.7222570532915361</v>
       </c>
       <c r="W2">
-        <v>0.04518209417411181</v>
+        <v>0.1084843818864472</v>
       </c>
       <c r="X2">
-        <v>0.06767837944928473</v>
+        <v>0.08002531722043218</v>
       </c>
       <c r="Y2">
-        <v>-0.02249628527517292</v>
+        <v>0.02845906466601501</v>
       </c>
       <c r="Z2">
-        <v>0.2313934147529383</v>
+        <v>0.5960277633577512</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05461016741541452</v>
+        <v>0.07544932816132421</v>
       </c>
       <c r="AC2">
-        <v>-0.05461016741541452</v>
+        <v>-0.07544932816132421</v>
       </c>
       <c r="AD2">
-        <v>249.3</v>
+        <v>185.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>249.3</v>
+        <v>185.7</v>
       </c>
       <c r="AG2">
-        <v>-441.4</v>
+        <v>-159.9</v>
       </c>
       <c r="AH2">
-        <v>0.3188387261798183</v>
+        <v>0.2795844625112918</v>
       </c>
       <c r="AI2">
-        <v>0.1987245914707055</v>
+        <v>0.1733084461035931</v>
       </c>
       <c r="AJ2">
-        <v>-4.839912280701755</v>
+        <v>-0.5018832391713748</v>
       </c>
       <c r="AK2">
-        <v>-0.7829017382050374</v>
+        <v>-0.2202782752445241</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Asia United Bank Corporation (PSE:AUB)</t>
+          <t>Philippine Business Bank, Inc. (PSE:PBB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07429999999999999</v>
+        <v>0.141</v>
       </c>
       <c r="E3">
-        <v>0.006500000000000001</v>
+        <v>0.241</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +728,82 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>43.4</v>
+        <v>22</v>
       </c>
       <c r="L3">
-        <v>0.2454751131221719</v>
+        <v>0.2294056308654849</v>
       </c>
       <c r="M3">
-        <v>19</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.0466143277723258</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.4377880184331797</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>19</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.0466143277723258</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.4377880184331797</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>402.4</v>
+        <v>169.7</v>
       </c>
       <c r="V3">
-        <v>0.987242394504416</v>
+        <v>1.439355385920271</v>
       </c>
       <c r="W3">
-        <v>0.05911195859438845</v>
+        <v>0.08202833706189411</v>
       </c>
       <c r="X3">
-        <v>0.06678955860687705</v>
+        <v>0.07659017794501788</v>
       </c>
       <c r="Y3">
-        <v>-0.0076776000124886</v>
+        <v>0.005438159116876229</v>
       </c>
       <c r="Z3">
-        <v>0.1876459350456378</v>
+        <v>1.76578898913644</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05459834425260704</v>
+        <v>0.07429222833222737</v>
       </c>
       <c r="AC3">
-        <v>-0.05459834425260704</v>
+        <v>-0.07429222833222737</v>
       </c>
       <c r="AD3">
-        <v>184.6</v>
+        <v>21.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>184.6</v>
+        <v>21.3</v>
       </c>
       <c r="AG3">
-        <v>-217.8</v>
+        <v>-148.4</v>
       </c>
       <c r="AH3">
-        <v>0.3117190138466734</v>
+        <v>0.1530172413793103</v>
       </c>
       <c r="AI3">
-        <v>0.2029686641011545</v>
+        <v>0.08198614318706697</v>
       </c>
       <c r="AJ3">
-        <v>-1.147523709167545</v>
+        <v>4.865573770491807</v>
       </c>
       <c r="AK3">
-        <v>-0.4295010845986984</v>
+        <v>-1.647058823529411</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Philippine Business Bank, Inc. (PSE:PBB)</t>
+          <t>Asia United Bank Corporation (PSE:AUB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,10 +829,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0616</v>
+        <v>0.115</v>
       </c>
       <c r="E4">
-        <v>-0.0858</v>
+        <v>0.168</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,82 +847,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>8.76</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="L4">
-        <v>0.1168</v>
+        <v>0.4549276039234003</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>16.5</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.04575707154742096</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.1694045174537988</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>16.5</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.04575707154742096</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.1694045174537988</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>288.3</v>
+        <v>175.9</v>
       </c>
       <c r="V4">
-        <v>2.3064</v>
+        <v>0.4877981142540211</v>
       </c>
       <c r="W4">
-        <v>0.03125222975383517</v>
+        <v>0.1349404267110003</v>
       </c>
       <c r="X4">
-        <v>0.06856720029169243</v>
+        <v>0.08346045649584651</v>
       </c>
       <c r="Y4">
-        <v>-0.03731497053785725</v>
+        <v>0.05147997021515378</v>
       </c>
       <c r="Z4">
-        <v>0.5137338173847522</v>
+        <v>0.4596393301846285</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05462199057822199</v>
+        <v>0.07660642799042106</v>
       </c>
       <c r="AC4">
-        <v>-0.05462199057822199</v>
+        <v>-0.07660642799042106</v>
       </c>
       <c r="AD4">
-        <v>64.7</v>
+        <v>164.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>64.7</v>
+        <v>164.4</v>
       </c>
       <c r="AG4">
-        <v>-223.6</v>
+        <v>-11.5</v>
       </c>
       <c r="AH4">
-        <v>0.3410648392198208</v>
+        <v>0.3131428571428572</v>
       </c>
       <c r="AI4">
-        <v>0.187536231884058</v>
+        <v>0.2025378834544783</v>
       </c>
       <c r="AJ4">
-        <v>2.267748478701825</v>
+        <v>-0.03294185047264394</v>
       </c>
       <c r="AK4">
-        <v>-3.943562610229278</v>
+        <v>-0.01808744888329664</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/philippines/philippines_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.128</v>
+        <v>0.10375</v>
       </c>
       <c r="E2">
-        <v>0.2045</v>
+        <v>0.136</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>119.4</v>
+        <v>237.665</v>
       </c>
       <c r="L2">
-        <v>0.3851612903225807</v>
+        <v>0.3732645432843322</v>
       </c>
       <c r="M2">
-        <v>16.5</v>
+        <v>44.76000000000001</v>
       </c>
       <c r="N2">
-        <v>0.03448275862068965</v>
+        <v>0.04524868580671251</v>
       </c>
       <c r="O2">
-        <v>0.1381909547738693</v>
+        <v>0.1883323164959081</v>
       </c>
       <c r="P2">
-        <v>16.5</v>
+        <v>44.76000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.03448275862068965</v>
+        <v>0.04524868580671251</v>
       </c>
       <c r="R2">
-        <v>0.1381909547738693</v>
+        <v>0.1883323164959081</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>345.6</v>
+        <v>460.63</v>
       </c>
       <c r="V2">
-        <v>0.7222570532915361</v>
+        <v>0.4656591184795795</v>
       </c>
       <c r="W2">
-        <v>0.1084843818864472</v>
+        <v>0.1183368422216733</v>
       </c>
       <c r="X2">
-        <v>0.08002531722043218</v>
+        <v>0.06221653459782788</v>
       </c>
       <c r="Y2">
-        <v>0.02845906466601501</v>
+        <v>0.05612030762384543</v>
       </c>
       <c r="Z2">
-        <v>0.5960277633577512</v>
+        <v>0.4556788091318973</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07544932816132421</v>
+        <v>0.06092381321734555</v>
       </c>
       <c r="AC2">
-        <v>-0.07544932816132421</v>
+        <v>-0.06092381321734555</v>
       </c>
       <c r="AD2">
-        <v>185.7</v>
+        <v>135.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>185.7</v>
+        <v>135.1</v>
       </c>
       <c r="AG2">
-        <v>-159.9</v>
+        <v>-325.53</v>
       </c>
       <c r="AH2">
-        <v>0.2795844625112918</v>
+        <v>0.1201636573868185</v>
       </c>
       <c r="AI2">
-        <v>0.1733084461035931</v>
+        <v>0.0689637570188872</v>
       </c>
       <c r="AJ2">
-        <v>-0.5018832391713748</v>
+        <v>-0.4904997965856525</v>
       </c>
       <c r="AK2">
-        <v>-0.2202782752445241</v>
+        <v>-0.2172560849456409</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Philippine Business Bank, Inc. (PSE:PBB)</t>
+          <t>Citystate Savings Bank, Inc. (PSE:CSB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.141</v>
-      </c>
-      <c r="E3">
-        <v>0.241</v>
+        <v>0.0965</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>22</v>
+        <v>-0.135</v>
       </c>
       <c r="L3">
-        <v>0.2294056308654849</v>
+        <v>-0.01979472140762463</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,7 +737,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,61 +746,61 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>169.7</v>
+        <v>5.53</v>
       </c>
       <c r="V3">
-        <v>1.439355385920271</v>
+        <v>0.2457777777777778</v>
       </c>
       <c r="W3">
-        <v>0.08202833706189411</v>
+        <v>-0.007031250000000001</v>
       </c>
       <c r="X3">
-        <v>0.07659017794501788</v>
+        <v>0.06041350547872495</v>
       </c>
       <c r="Y3">
-        <v>0.005438159116876229</v>
+        <v>-0.06744475547872494</v>
       </c>
       <c r="Z3">
-        <v>1.76578898913644</v>
+        <v>0.4405684754521965</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07429222833222737</v>
+        <v>0.06041350547872495</v>
       </c>
       <c r="AC3">
-        <v>-0.07429222833222737</v>
+        <v>-0.06041350547872495</v>
       </c>
       <c r="AD3">
-        <v>21.3</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>21.3</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-148.4</v>
+        <v>-5.53</v>
       </c>
       <c r="AH3">
-        <v>0.1530172413793103</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.08198614318706697</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>4.865573770491807</v>
+        <v>-0.3258691809074838</v>
       </c>
       <c r="AK3">
-        <v>-1.647058823529411</v>
+        <v>-0.3378130726939524</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -820,117 +817,361 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Philippine Savings Bank (PSE:PSB)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0231</v>
+      </c>
+      <c r="E4">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="L4">
+        <v>0.3041871921182266</v>
+      </c>
+      <c r="M4">
+        <v>22.6</v>
+      </c>
+      <c r="N4">
+        <v>0.05533790401567092</v>
+      </c>
+      <c r="O4">
+        <v>0.3049932523616735</v>
+      </c>
+      <c r="P4">
+        <v>22.6</v>
+      </c>
+      <c r="Q4">
+        <v>0.05533790401567092</v>
+      </c>
+      <c r="R4">
+        <v>0.3049932523616735</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>58</v>
+      </c>
+      <c r="V4">
+        <v>0.1420176297747307</v>
+      </c>
+      <c r="W4">
+        <v>0.1182006699633115</v>
+      </c>
+      <c r="X4">
+        <v>0.06169951963918777</v>
+      </c>
+      <c r="Y4">
+        <v>0.05650115032412376</v>
+      </c>
+      <c r="Z4">
+        <v>0.3510086455331412</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.06079103761529676</v>
+      </c>
+      <c r="AC4">
+        <v>-0.06079103761529676</v>
+      </c>
+      <c r="AD4">
+        <v>32.4</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>32.4</v>
+      </c>
+      <c r="AG4">
+        <v>-25.6</v>
+      </c>
+      <c r="AH4">
+        <v>0.07350272232304901</v>
+      </c>
+      <c r="AI4">
+        <v>0.04428044280442805</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.06687565308254964</v>
+      </c>
+      <c r="AK4">
+        <v>-0.03799910939587354</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Asia United Bank Corporation (PSE:AUB)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.115</v>
-      </c>
-      <c r="E4">
-        <v>0.168</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="L4">
-        <v>0.4549276039234003</v>
-      </c>
-      <c r="M4">
-        <v>16.5</v>
-      </c>
-      <c r="N4">
-        <v>0.04575707154742096</v>
-      </c>
-      <c r="O4">
-        <v>0.1694045174537988</v>
-      </c>
-      <c r="P4">
-        <v>16.5</v>
-      </c>
-      <c r="Q4">
-        <v>0.04575707154742096</v>
-      </c>
-      <c r="R4">
-        <v>0.1694045174537988</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>175.9</v>
-      </c>
-      <c r="V4">
-        <v>0.4877981142540211</v>
-      </c>
-      <c r="W4">
-        <v>0.1349404267110003</v>
-      </c>
-      <c r="X4">
-        <v>0.08346045649584651</v>
-      </c>
-      <c r="Y4">
-        <v>0.05147997021515378</v>
-      </c>
-      <c r="Z4">
-        <v>0.4596393301846285</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.07660642799042106</v>
-      </c>
-      <c r="AC4">
-        <v>-0.07660642799042106</v>
-      </c>
-      <c r="AD4">
-        <v>164.4</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>164.4</v>
-      </c>
-      <c r="AG4">
-        <v>-11.5</v>
-      </c>
-      <c r="AH4">
-        <v>0.3131428571428572</v>
-      </c>
-      <c r="AI4">
-        <v>0.2025378834544783</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.03294185047264394</v>
-      </c>
-      <c r="AK4">
-        <v>-0.01808744888329664</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="D5">
+        <v>0.135</v>
+      </c>
+      <c r="E5">
+        <v>0.218</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>136.7</v>
+      </c>
+      <c r="L5">
+        <v>0.4951104672220209</v>
+      </c>
+      <c r="M5">
+        <v>17.1</v>
+      </c>
+      <c r="N5">
+        <v>0.03979520595764487</v>
+      </c>
+      <c r="O5">
+        <v>0.1250914411119239</v>
+      </c>
+      <c r="P5">
+        <v>17.1</v>
+      </c>
+      <c r="Q5">
+        <v>0.03979520595764487</v>
+      </c>
+      <c r="R5">
+        <v>0.1250914411119239</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>216</v>
+      </c>
+      <c r="V5">
+        <v>0.5026762857807773</v>
+      </c>
+      <c r="W5">
+        <v>0.2121024049650892</v>
+      </c>
+      <c r="X5">
+        <v>0.062733549556468</v>
+      </c>
+      <c r="Y5">
+        <v>0.1493688554086212</v>
+      </c>
+      <c r="Z5">
+        <v>0.4603201067022342</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.06105658881939435</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06105658881939435</v>
+      </c>
+      <c r="AD5">
+        <v>61.5</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>61.5</v>
+      </c>
+      <c r="AG5">
+        <v>-154.5</v>
+      </c>
+      <c r="AH5">
+        <v>0.1252035830618893</v>
+      </c>
+      <c r="AI5">
+        <v>0.07113938692886061</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.5614098837209303</v>
+      </c>
+      <c r="AK5">
+        <v>-0.2382420971472629</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Philippine Business Bank, Inc. (PSE:PBB)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.111</v>
+      </c>
+      <c r="E6">
+        <v>0.136</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>27</v>
+      </c>
+      <c r="L6">
+        <v>0.2450090744101633</v>
+      </c>
+      <c r="M6">
+        <v>5.06</v>
+      </c>
+      <c r="N6">
+        <v>0.03934681181959564</v>
+      </c>
+      <c r="O6">
+        <v>0.1874074074074074</v>
+      </c>
+      <c r="P6">
+        <v>5.06</v>
+      </c>
+      <c r="Q6">
+        <v>0.03934681181959564</v>
+      </c>
+      <c r="R6">
+        <v>0.1874074074074074</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>181.1</v>
+      </c>
+      <c r="V6">
+        <v>1.408242612752722</v>
+      </c>
+      <c r="W6">
+        <v>0.1184730144800351</v>
+      </c>
+      <c r="X6">
+        <v>0.06560679723061143</v>
+      </c>
+      <c r="Y6">
+        <v>0.05286621724942367</v>
+      </c>
+      <c r="Z6">
+        <v>1.251988184503522</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.06271743020334565</v>
+      </c>
+      <c r="AC6">
+        <v>-0.06271743020334565</v>
+      </c>
+      <c r="AD6">
+        <v>41.2</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>41.2</v>
+      </c>
+      <c r="AG6">
+        <v>-139.9</v>
+      </c>
+      <c r="AH6">
+        <v>0.2426383981154299</v>
+      </c>
+      <c r="AI6">
+        <v>0.1208565561748313</v>
+      </c>
+      <c r="AJ6">
+        <v>12.38053097345134</v>
+      </c>
+      <c r="AK6">
+        <v>-0.8754693366708384</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
         <v>0</v>
       </c>
     </row>
